--- a/디자인가이드/레이아웃_가이드.xlsx
+++ b/디자인가이드/레이아웃_가이드.xlsx
@@ -5,99 +5,139 @@
   <x:workbookPr date1904="0" showBorderUnselectedTables="1" filterPrivacy="0" promptedSolutions="0" showInkAnnotation="1" backupFile="0" saveExternalLinkValues="1" codeName="ThisWorkbook" hidePivotFieldList="0" allowRefreshQuery="0" publishItems="0" checkCompatibility="0" autoCompressPictures="1" refreshAllConnections="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\glim0\OneDrive\문서\Claude\Projects\02. 웹기획자\판매용_템플릿\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\glim0\OneDrive\문서\Claude\Projects\02. 웹기획자\디자인가이드\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="15084" windowHeight="14328" tabRatio="500"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="15084" windowHeight="12408" tabRatio="500"/>
   </x:bookViews>
   <x:sheets>
-    <x:sheet name="Sheet1" sheetId="1" r:id="rId4"/>
+    <x:sheet name="레이아웃 컨셉" sheetId="1" r:id="rId4"/>
+    <x:sheet name="컴포넌트" sheetId="2" r:id="rId5"/>
   </x:sheets>
   <x:calcPr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" mc:Ignorable="hs" hs:hclCalcId="904"/>
 </x:workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
+  <x:si>
+    <x:t xml:space="preserve">콘텐츠 그룹 </x:t>
+  </x:si>
+  <x:si>
+    <x:t>테이블 및 리스트 내 버튼 : 아래 라인 또는 텍스트만 노출, 폰트사이즈 12, 가로는 폰트 길이 + 패딩 12px , 높이 폰트 사이즈+패딩 8px</x:t>
+  </x:si>
+  <x:si>
+    <x:t>화면 전체를 하나의 이미지나 영상으로 채우는 방식입니다. 첫인상에서 강한 시각적 임팩트를 전달할 수 있으며, 브랜드의 분위기를 즉각적으로 전달합니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.figma.com/design/1eRM3NMwD3I0Fv0FkP2OzS/coffeine-color_Block-conponents--%EB%B3%B5%EC%82%AC-?node-id=12-54943&amp;m=dev</x:t>
+  </x:si>
+  <x:si>
+    <x:t>한 줄 리스트 형 내 내용별 위아래 간격 : 컴팩트 4px, 넉넉 8PX</x:t>
+  </x:si>
+  <x:si>
+    <x:t>주요 버튼 : 풀컬러, 폰트사이즈 14, 가로는 폰트 길이 + 패딩 12px , 높이 폰트 사이즈+패딩 8px</x:t>
+  </x:si>
+  <x:si>
+    <x:t>보조 버튼 : full 테두리, 폰트사이즈 14, 가로는 폰트 길이 + 패딩 12px , 높이 폰트 사이즈+패딩 8px</x:t>
+  </x:si>
+  <x:si>
+    <x:t>적합한 사이트: 뉴스 사이트, 포트폴리오, 제품 비교 페이지</x:t>
+  </x:si>
+  <x:si>
+    <x:t>장점: 구조가 단순하여 가독성이 높고, 반응형 대응이 쉽습니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>적합한 사이트: 포트폴리오 갤러리, 쇼핑몰 상품 목록, 팀 소개</x:t>
+  </x:si>
+  <x:si>
+    <x:t>적합한 사이트: 랜딩페이지, 블로그, 스토리텔링형 소개 페이지</x:t>
+  </x:si>
+  <x:si>
+    <x:t>장점: 몰입감이 높고, 브랜드 이미지를 강렬하게 전달합니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>배지 : 풀컬러(미리보기에 나온컬러 유지), 폰트사이즈 11, 가로는 폰트 길이 + 패딩 6px , 높이 폰트 사이즈+패딩 4px</x:t>
+  </x:si>
+  <x:si>
+    <x:t>콘텐츠 단락 위아래 간격 : 컴팩트 48px, 넉넉 80PX</x:t>
+  </x:si>
+  <x:si>
+    <x:t>테이블 : 폰트사이즈 14, 가로는 폰트 길이 + 패딩 8px , 높이 폰트 사이즈+패딩 8px</x:t>
+  </x:si>
+  <x:si>
+    <x:t>콘텐츠 영역은 1440에 좌우 패딩값 24</x:t>
+  </x:si>
+  <x:si>
+    <x:t>컴포넌트 규칙(참고 피그마)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>박스 형 내 내 내용별 위아래 간격 : 컴팩트 4px, 넉넉 8PX</x:t>
+  </x:si>
+  <x:si>
+    <x:t>콘텐츠 그룹 간 좌우 간격 : 16px</x:t>
+  </x:si>
   <x:si>
     <x:t>왼쪽 또는 오른쪽에 고정 영역(사이드바)을 두고, 나머지 공간에 메인 콘텐츠를 배치하는 방식입니다. 사이드바에는 내비게이션 메뉴, 카테고리, 최신 글 목록 등을 배치합니다.</x:t>
   </x:si>
   <x:si>
+    <x:t>장점: 메뉴 접근성이 높아 콘텐츠 탐색이 편리합니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>적합한 사이트: 블로그, 문서(Documentation) 사이트, 관리자 페이지</x:t>
+  </x:si>
+  <x:si>
+    <x:t>풀스크린 레이아웃 (Full Screen)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>화면 중앙에 하나의 열로 콘텐츠를 순차적으로 배치하는 방식입니다. 위에서 아래로 스크롤하면서 정보를 자연스럽게 읽어나가는 구조로, 모바일 환경에 최적화되어 있습니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>벤토 그리드 레이아웃 (Bento Grid)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>멀티 컬럼 레이아웃 (Multi Column)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>싱글 컬럼 레이아웃 (Single Column)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>화면을 2~3개의 열로 나누어 콘텐츠를 병렬 배치하는 방식입니다. 한 화면에 여러 정보를 동시에 보여줄 수 있어, 콘텐츠 양이 많은 사이트에 적합합니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>적합한 사이트: 브랜드 사이트, 크리에이티브 에이전시, 호텔·리조트 사이트</x:t>
+  </x:si>
+  <x:si>
+    <x:t>장점: 시각적 통일감이 뛰어나고, 다량의 아이템을 정돈되게 보여줍니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>적합한 사이트: 서비스 소개 페이지, 기능 안내, 대시보드형 페이지</x:t>
+  </x:si>
+  <x:si>
+    <x:t>장점: 정보 밀도가 높고, 비교형 콘텐츠를 효과적으로 전달합니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>장점: 정보의 우선순위를 직관적으로 표현하며, 현대적인 인상을 줍니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>동일한 크기의 격자 안에 콘텐츠를 배치하는 방식입니다. 정돈되고 균형 잡힌 인상을 주며, 이미지 중심 콘텐츠에 적합합니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>사이드바 레이아웃 (Sidebar)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그리드 레이아웃 (Grid)</x:t>
+  </x:si>
+  <x:si>
     <x:t>다양한 크기의 카드 블록을 조합하여 배치하는 레이아웃입니다. 일반 그리드와 달리 블록 크기가 다르기 때문에, 중요한 콘텐츠를 크게, 보조 콘텐츠를 작게 표현하여 정보의 위계를 시각적으로 전달합니다. 2024~2025년 주요 웹디자인 트렌드 중 하나입니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>풀스크린 레이아웃 (Full Screen)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그리드 레이아웃 (Grid)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>장점: 정보 밀도가 높고, 비교형 콘텐츠를 효과적으로 전달합니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>장점: 시각적 통일감이 뛰어나고, 다량의 아이템을 정돈되게 보여줍니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>장점: 정보의 우선순위를 직관적으로 표현하며, 현대적인 인상을 줍니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>적합한 사이트: 서비스 소개 페이지, 기능 안내, 대시보드형 페이지</x:t>
-  </x:si>
-  <x:si>
-    <x:t>동일한 크기의 격자 안에 콘텐츠를 배치하는 방식입니다. 정돈되고 균형 잡힌 인상을 주며, 이미지 중심 콘텐츠에 적합합니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>멀티 컬럼 레이아웃 (Multi Column)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>싱글 컬럼 레이아웃 (Single Column)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>벤토 그리드 레이아웃 (Bento Grid)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>적합한 사이트: 뉴스 사이트, 포트폴리오, 제품 비교 페이지</x:t>
-  </x:si>
-  <x:si>
-    <x:t>장점: 구조가 단순하여 가독성이 높고, 반응형 대응이 쉽습니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>적합한 사이트: 랜딩페이지, 블로그, 스토리텔링형 소개 페이지</x:t>
-  </x:si>
-  <x:si>
-    <x:t>적합한 사이트: 포트폴리오 갤러리, 쇼핑몰 상품 목록, 팀 소개</x:t>
-  </x:si>
-  <x:si>
-    <x:t>장점: 몰입감이 높고, 브랜드 이미지를 강렬하게 전달합니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>적합한 사이트: 브랜드 사이트, 크리에이티브 에이전시, 호텔·리조트 사이트</x:t>
-  </x:si>
-  <x:si>
-    <x:t>화면 중앙에 하나의 열로 콘텐츠를 순차적으로 배치하는 방식입니다. 위에서 아래로 스크롤하면서 정보를 자연스럽게 읽어나가는 구조로, 모바일 환경에 최적화되어 있습니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>사이드바 레이아웃 (Sidebar)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>화면을 2~3개의 열로 나누어 콘텐츠를 병렬 배치하는 방식입니다. 한 화면에 여러 정보를 동시에 보여줄 수 있어, 콘텐츠 양이 많은 사이트에 적합합니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>화면 전체를 하나의 이미지나 영상으로 채우는 방식입니다. 첫인상에서 강한 시각적 임팩트를 전달할 수 있으며, 브랜드의 분위기를 즉각적으로 전달합니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>적합한 사이트: 블로그, 문서(Documentation) 사이트, 관리자 페이지</x:t>
-  </x:si>
-  <x:si>
-    <x:t>장점: 메뉴 접근성이 높아 콘텐츠 탐색이 편리합니다.</x:t>
   </x:si>
 </x:sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="7">
+  <x:fonts count="8">
     <x:font>
       <x:name val="맑은 고딕"/>
       <x:sz val="11"/>
@@ -134,6 +174,27 @@
       <x:color rgb="ff000000"/>
       <x:b val="1"/>
     </x:font>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:font hs:extension="1">
+          <x:name val="맑은 고딕"/>
+          <x:sz val="11"/>
+          <x:color rgb="ff0000ff"/>
+          <x:u/>
+          <hs:underlineType val="1"/>
+          <hs:underlineShape val="solid"/>
+          <hs:underlineColor rgb="ff0000ff"/>
+        </x:font>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:font>
+          <x:name val="맑은 고딕"/>
+          <x:sz val="11"/>
+          <x:color rgb="ff0000ff"/>
+          <x:u/>
+        </x:font>
+      </mc:Fallback>
+    </mc:AlternateContent>
   </x:fonts>
   <x:fills count="2">
     <x:fill>
@@ -164,7 +225,7 @@
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="3">
+  <x:cellXfs count="6">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
@@ -173,6 +234,25 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" hs:applyExtension="1">
+          <x:alignment horizontal="left" vertical="center" indent="1"/>
+          <hs:parashape hs:leftMargin="1134" hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
+        </x:xf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+          <x:alignment horizontal="left" vertical="center" indent="1"/>
+        </x:xf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -903,125 +983,220 @@
   <x:sheetData>
     <x:row r="1" spans="2:2">
       <x:c r="B1" s="2" t="s">
-        <x:v>10</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="2:2" ht="49.14999999999999857891">
       <x:c r="B2" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="2:2">
       <x:c r="B3" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="2:2">
       <x:c r="B4" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="2:2">
       <x:c r="B6" s="2" t="s">
-        <x:v>9</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="2:2" ht="32.75">
       <x:c r="B7" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="2:2">
       <x:c r="B8" s="1" t="s">
-        <x:v>4</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="2:2">
       <x:c r="B9" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="2:2">
       <x:c r="B11" s="2" t="s">
-        <x:v>3</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="2:2" ht="32.75">
       <x:c r="B12" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="2:2">
       <x:c r="B13" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="2:2">
       <x:c r="B14" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="2:2">
       <x:c r="B16" s="2" t="s">
-        <x:v>11</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="2:2" ht="65.5">
       <x:c r="B17" s="1" t="s">
-        <x:v>1</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="2:2">
       <x:c r="B18" s="1" t="s">
-        <x:v>6</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="2:2">
       <x:c r="B19" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="2:2">
       <x:c r="B21" s="2" t="s">
-        <x:v>19</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="2:2" ht="49.14999999999999857891">
       <x:c r="B22" s="1" t="s">
-        <x:v>0</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="2:2">
       <x:c r="B23" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="2:2">
       <x:c r="B24" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="2:2">
       <x:c r="B26" s="2" t="s">
-        <x:v>2</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="2:2" ht="32.75">
       <x:c r="B27" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="2:2">
       <x:c r="B28" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="2:2">
       <x:c r="B29" s="1" t="s">
+        <x:v>28</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.74805557727813720703" right="0.74805557727813720703" top="0.98430556058883666992" bottom="0.98430556058883666992" header="0.51166665554046630859" footer="0.51166665554046630859"/>
+  <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="0" fitToHeight="0" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="0" verticalDpi="0" copies="1"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetPr codeName="Sheet2"/>
+  <x:dimension ref="A2:A20"/>
+  <x:sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="16.39999999999999857891"/>
+  <x:cols>
+    <x:col min="1" max="1" width="77.19921875" style="3" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="2" spans="1:1">
+      <x:c r="A2" s="4" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:1">
+      <x:c r="A3" s="5" t="s">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:1">
+      <x:c r="A5" s="4" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:1">
+      <x:c r="A6" s="4" t="s">
+        <x:v>13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:1">
+      <x:c r="A7" s="4" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:1">
+      <x:c r="A8" s="4"/>
+    </x:row>
+    <x:row r="9" spans="1:1">
+      <x:c r="A9" s="4" t="s">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:1">
+      <x:c r="A10" s="4" t="s">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:1">
+      <x:c r="A11" s="4" t="s">
         <x:v>17</x:v>
       </x:c>
     </x:row>
+    <x:row r="12" spans="1:1">
+      <x:c r="A12" s="4"/>
+    </x:row>
+    <x:row r="13" spans="1:1">
+      <x:c r="A13" s="4" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:1">
+      <x:c r="A14" s="4"/>
+    </x:row>
+    <x:row r="15" spans="1:1">
+      <x:c r="A15" s="4" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:1">
+      <x:c r="A16" s="4" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:1">
+      <x:c r="A17" s="4" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:1">
+      <x:c r="A19" s="4" t="s">
+        <x:v>14</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:1">
+      <x:c r="A20" s="4"/>
+    </x:row>
   </x:sheetData>
+  <x:hyperlinks>
+    <x:hyperlink ref="A3:A3" r:id="rId1"/>
+  </x:hyperlinks>
   <x:pageMargins left="0.74805557727813720703" right="0.74805557727813720703" top="0.98430556058883666992" bottom="0.98430556058883666992" header="0.51180553436279296875" footer="0.51180553436279296875"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="0" fitToHeight="0" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="0" verticalDpi="0" copies="1"/>
 </x:worksheet>
